--- a/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
+++ b/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,13 +448,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DMI0009590352</v>
+        <v>DMI0009701001</v>
       </c>
       <c r="B2" t="str">
-        <v>1174</v>
+        <v>1166</v>
       </c>
       <c r="C2" t="str">
-        <v>ss</v>
+        <v>Yes</v>
       </c>
       <c r="D2" t="str">
         <v>PTP</v>
@@ -466,42 +466,21 @@
         <v>2025/12/26</v>
       </c>
       <c r="G2">
-        <v>98</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+        <v>62</v>
       </c>
       <c r="I2" t="str">
-        <v>Bulk upload Aug29</v>
-      </c>
-      <c r="J2" t="str">
-        <v>6281449869</v>
-      </c>
-      <c r="K2" t="str">
-        <v>btm</v>
-      </c>
-      <c r="L2" t="str">
-        <v>banglore</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Treva.Runolfsson@hotmail.com</v>
-      </c>
-      <c r="N2" t="str">
-        <v>permanent</v>
-      </c>
-      <c r="O2" t="str">
-        <v>new</v>
+        <v>Approved Agency agent</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DMI0009590352</v>
+        <v>DMI0009701002</v>
       </c>
       <c r="B3" t="str">
-        <v>118974</v>
+        <v>2005</v>
       </c>
       <c r="C3" t="str">
-        <v>ss</v>
+        <v>Yes</v>
       </c>
       <c r="D3" t="str">
         <v>PTP</v>
@@ -513,37 +492,68 @@
         <v>2025/12/26</v>
       </c>
       <c r="G3">
-        <v>98</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
+        <v>62</v>
       </c>
       <c r="I3" t="str">
-        <v>Bulk upload Aug29</v>
-      </c>
-      <c r="J3" t="str">
-        <v>6281449869</v>
-      </c>
-      <c r="K3" t="str">
-        <v>btm</v>
-      </c>
-      <c r="L3" t="str">
-        <v>banglore</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Treva.Runolfsson@hotmail.com</v>
-      </c>
-      <c r="N3" t="str">
-        <v>permanent</v>
-      </c>
-      <c r="O3" t="str">
-        <v>new</v>
+        <v>Rejected Agency agent</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DMI0009701003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>787868</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D4" t="str">
+        <v>PTP</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PTP</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2025/12/26</v>
+      </c>
+      <c r="G4">
+        <v>62</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Approved Staff agent</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DMI0009701004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2003</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D5" t="str">
+        <v>PTP</v>
+      </c>
+      <c r="E5" t="str">
+        <v>PTP</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2025/12/26</v>
+      </c>
+      <c r="G5">
+        <v>62</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Pending Staff agent</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
+++ b/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -32,8 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -397,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,10 +412,10 @@
         <v>RightPartyContact</v>
       </c>
       <c r="D1" t="str">
-        <v>Action Code</v>
+        <v>DispositionCodeGroup</v>
       </c>
       <c r="E1" t="str">
-        <v>ResultCode</v>
+        <v>DispositionCode</v>
       </c>
       <c r="F1" t="str">
         <v>Next Action Date</v>
@@ -466,7 +468,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G2">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="I2" t="str">
         <v>Approved Agency agent</v>
@@ -492,7 +494,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G3">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="I3" t="str">
         <v>Rejected Agency agent</v>
@@ -518,7 +520,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G4">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="I4" t="str">
         <v>Approved Staff agent</v>
@@ -544,16 +546,15 @@
         <v>2025/12/26</v>
       </c>
       <c r="G5">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
         <v>Pending Staff agent</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
+++ b/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
@@ -468,7 +468,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I2" t="str">
         <v>Approved Agency agent</v>
@@ -494,7 +494,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I3" t="str">
         <v>Rejected Agency agent</v>
@@ -520,7 +520,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I4" t="str">
         <v>Approved Staff agent</v>
@@ -546,7 +546,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I5" t="str">
         <v>Pending Staff agent</v>

--- a/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
+++ b/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
@@ -468,7 +468,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I2" t="str">
         <v>Approved Agency agent</v>
@@ -494,7 +494,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I3" t="str">
         <v>Rejected Agency agent</v>
@@ -520,7 +520,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I4" t="str">
         <v>Approved Staff agent</v>
@@ -546,7 +546,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" t="str">
         <v>Pending Staff agent</v>

--- a/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
+++ b/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
@@ -468,7 +468,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="I2" t="str">
         <v>Approved Agency agent</v>
@@ -494,7 +494,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="I3" t="str">
         <v>Rejected Agency agent</v>
@@ -520,7 +520,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G4">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="I4" t="str">
         <v>Approved Staff agent</v>
@@ -546,7 +546,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G5">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="I5" t="str">
         <v>Pending Staff agent</v>

--- a/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
+++ b/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
@@ -468,7 +468,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I2" t="str">
         <v>Approved Agency agent</v>
@@ -494,7 +494,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I3" t="str">
         <v>Rejected Agency agent</v>
@@ -520,7 +520,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G4">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I4" t="str">
         <v>Approved Staff agent</v>
@@ -546,7 +546,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G5">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I5" t="str">
         <v>Pending Staff agent</v>

--- a/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
+++ b/November_Release_SCB/Cypress/fixtures/Bulktrail.xlsx
@@ -468,7 +468,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G2">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I2" t="str">
         <v>Approved Agency agent</v>
@@ -494,7 +494,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G3">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I3" t="str">
         <v>Rejected Agency agent</v>
@@ -520,7 +520,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G4">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I4" t="str">
         <v>Approved Staff agent</v>
@@ -546,7 +546,7 @@
         <v>2025/12/26</v>
       </c>
       <c r="G5">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I5" t="str">
         <v>Pending Staff agent</v>
